--- a/driver_forms/002_vehicle_registration_form--driver_forms.xlsx
+++ b/driver_forms/002_vehicle_registration_form--driver_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -949,8 +949,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -978,12 +978,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'vehicle_1'}</t>
+          <t>vehicle_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Vehicle 1'}</t>
+          <t>Vehicle 1</t>
         </is>
       </c>
     </row>
@@ -995,12 +995,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'vehicle_2'}</t>
+          <t>vehicle_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Vehicle 2'}</t>
+          <t>Vehicle 2</t>
         </is>
       </c>
     </row>
@@ -1012,12 +1012,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'vehicle_3'}</t>
+          <t>vehicle_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Vehicle 3'}</t>
+          <t>Vehicle 3</t>
         </is>
       </c>
     </row>
@@ -1029,12 +1029,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1046,12 +1046,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1063,12 +1063,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1080,12 +1080,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'car'}</t>
+          <t>car</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Car'}</t>
+          <t>Car</t>
         </is>
       </c>
     </row>
@@ -1097,12 +1097,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'motorcycle'}</t>
+          <t>motorcycle</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Motorcycle'}</t>
+          <t>Motorcycle</t>
         </is>
       </c>
     </row>
@@ -1114,12 +1114,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'truck'}</t>
+          <t>truck</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Truck'}</t>
+          <t>Truck</t>
         </is>
       </c>
     </row>
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'red'}</t>
+          <t>red</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Red'}</t>
+          <t>Red</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'blue'}</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Blue'}</t>
+          <t>Blue</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'green'}</t>
+          <t>green</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Green'}</t>
+          <t>Green</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'registered'}</t>
+          <t>registered</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Registered'}</t>
+          <t>Registered</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'unregistered'}</t>
+          <t>unregistered</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Unregistered'}</t>
+          <t>Unregistered</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
